--- a/livrables/blocs_urbains.xlsx
+++ b/livrables/blocs_urbains.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HYPOTHÈSE : fenêtre km, traversée au plafond S1 ∧ bande</t>
+          <t>HYPOTHÈSE : fenêtre km, traversée au plafond du scénario de base ∧ bande</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HYPOTHÈSE : fenêtre km, traversée au plafond S1 ∧ bande</t>
+          <t>HYPOTHÈSE : fenêtre km, traversée au plafond du scénario de base ∧ bande</t>
         </is>
       </c>
     </row>

--- a/livrables/blocs_urbains.xlsx
+++ b/livrables/blocs_urbains.xlsx
@@ -484,24 +484,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Montréal Central ↔ Saint-Lambert (pont Victoria)</t>
+          <t>Montréal Central ↔ pont Victoria (culée sud)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6.11</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SOURCE : GTFS VIA (médiane des sillons)</t>
+          <t>SOURCE : GTFS VIA (médiane des sillons) moins l'approche de gare hors bloc au profil du train actuel</t>
         </is>
       </c>
     </row>
@@ -513,20 +513,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sainte-Foy ↔ Québec (pont de Québec)</t>
+          <t>Charny ↔ Québec (pont de Québec, gare du Palais)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>249.98</v>
+        <v>245.04</v>
       </c>
       <c r="D3" t="n">
         <v>269.85</v>
       </c>
       <c r="E3" t="n">
-        <v>19.9</v>
+        <v>24.8</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
